--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena_provincial.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2021_magallanes_y_la_antartica_chilena_provincial.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 01:21</t>
+    <t xml:space="preserve">2026-10-05 05:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Magallanes y la Antartica Chilena</t>
+    <t xml:space="preserve">Region de Magallanes</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
